--- a/FinalReport/Evidence/wav2vec_vs_mfcc.xlsx
+++ b/FinalReport/Evidence/wav2vec_vs_mfcc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cianan/Documents/College/GitHub/FYP/FinalReport/Evidence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795312E2-C880-554D-BBEB-3F8426961CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097B70FD-1339-C64F-B29F-58CF912393EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="2060" windowWidth="27240" windowHeight="16440" xr2:uid="{9FB7942C-3D07-AE46-963A-716438D52045}"/>
   </bookViews>
@@ -135,7 +135,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{70F92EB6-4E2C-E14F-A798-1CD5BBFB705E}" name="Table1" displayName="Table1" ref="B3:G9" totalsRowShown="0">
-  <autoFilter ref="B3:G9" xr:uid="{70F92EB6-4E2C-E14F-A798-1CD5BBFB705E}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{A609B868-A3B3-0548-ABE0-56D8B2C21991}" name="TASK"/>
     <tableColumn id="2" xr3:uid="{866AEE98-2742-CC40-BE12-BDFF1338B04E}" name="MFCC BA"/>
